--- a/tools/xlsform_samples/AUDIT.xlsx
+++ b/tools/xlsform_samples/AUDIT.xlsx
@@ -948,7 +948,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>alcohol_use (sum_coded) - Sum of all items (0-40). Score ≥8 = hazardous use; ≥15 = dependence likely.</t>
+          <t>alcohol_use (sum_coded) - Sum of all items (0-40). Score &gt;=8 = hazardous use; &gt;=15 = dependence likely.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>

--- a/tools/xlsform_samples/AUDIT.xlsx
+++ b/tools/xlsform_samples/AUDIT.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -908,84 +908,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AUDIT_scoring</t>
+          <t>AUDIT_alcohol_use</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Computed Scores</t>
+          <t>alcohol_use (sum_coded) - Sum of all items (0-40). Score &gt;=8 = hazardous use; &gt;=15 = dependence likely.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>${audit1} + ${audit2} + ${audit3} + ${audit4} + ${audit5} + ${audit6} + ${audit7} + ${audit8} + ${audit9} + ${audit10}</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>AUDIT_alcohol_use</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>alcohol_use (sum_coded) - Sum of all items (0-40). Score &gt;=8 = hazardous use; &gt;=15 = dependence likely.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>${audit1} + ${audit2} + ${audit3} + ${audit4} + ${audit5} + ${audit6} + ${audit7} + ${audit8} + ${audit9} + ${audit10}</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>AUDIT_scoring</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/xlsform_samples/AUDIT.xlsx
+++ b/tools/xlsform_samples/AUDIT.xlsx
@@ -1216,7 +1216,11 @@
           <t>20260618</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>English (en)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
